--- a/p6_deployment/data/italy/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/italy/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,343 +475,1521 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>id_country</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>coach_home</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>coach_away</t>
+          <t>season</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>id_country</t>
+          <t>country</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
+          <t>competition</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4W5t03Zl</t>
+          <t>O2Fteteo</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45438.65625</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">massa d   ita </t>
-        </is>
-      </c>
+        <v>45521.5625</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio carlo castellani  empoli </t>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16284</v>
+        <v>36599</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>as roma</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>MLVBCoYg</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>nicola davide</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>xjigzK81</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>de rossi daniele</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>77</v>
-      </c>
-      <c r="O2" t="n">
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>77</v>
+      </c>
+      <c r="K2" t="n">
         <v>771</v>
       </c>
-      <c r="P2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>20232024</v>
+      <c r="M2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rN4paNle</t>
+          <t>Sf88FVcc</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45438.65625</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">doveri d   ita </t>
-        </is>
-      </c>
+        <v>45521.5625</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio benito stirpe  frosinone </t>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16227</v>
+        <v>27906</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pfo9H1Wp</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>frosinone</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>udinese</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>n10g3KfJ</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>di francesco eusebio</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>A1CicVEU</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>cannavaro fabio</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>77</v>
-      </c>
-      <c r="O3" t="n">
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>77</v>
+      </c>
+      <c r="K3" t="n">
         <v>771</v>
       </c>
-      <c r="P3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>20232024</v>
+      <c r="M3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6Le197C2</t>
+          <t>0lGMiS5j</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45438.65625</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tremolada p   ita </t>
-        </is>
-      </c>
+        <v>45521.65625</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio olimpico  rome </t>
+          <t xml:space="preserve">stadio giuseppe meazza  san siro 
+  milan </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>70634</v>
+        <v>80018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>QDdvI0zl</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>sassuolo</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Qu12kvXf</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>tudor igor</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>AcgUMf0E</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>ballardini davide</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>77</v>
-      </c>
-      <c r="O4" t="n">
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>77</v>
+      </c>
+      <c r="K4" t="n">
         <v>771</v>
       </c>
-      <c r="P4" t="n">
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>20232024</v>
+      <c r="M4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jPP565dL</t>
+          <t>hKOA02XN</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45438.65625</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zufferli l   ita </t>
-        </is>
-      </c>
+        <v>45521.65625</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio marc antonio bentegodi  verona </t>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
         </is>
       </c>
       <c r="E5" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>77</v>
+      </c>
+      <c r="K5" t="n">
+        <v>771</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>4xHh663n</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45522.5625</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio renato dall ara
+  bologna </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>38279</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>77</v>
+      </c>
+      <c r="K6" t="n">
+        <v>771</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6RvR2hEi</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45522.5625</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marc antonio bentegodi
+  verona </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>39211</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>rJVAIaHo</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>verona</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>inter</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>S8Ygn9ME</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>baroni marco</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>j32a3mqs</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>inzaghi simone</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>77</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>77</v>
+      </c>
+      <c r="K7" t="n">
         <v>771</v>
       </c>
-      <c r="P5" t="n">
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>20232024</v>
+      <c r="M7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>YH892O2B</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unipol domus
+  cagliari </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>16416</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>77</v>
+      </c>
+      <c r="K8" t="n">
+        <v>771</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8jyraADG</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45522.65625</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico
+  rome </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>70634</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>77</v>
+      </c>
+      <c r="K9" t="n">
+        <v>771</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45507.54166666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dei marmi
+  carrara </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5280</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>carrarese</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4rwnnbnB</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>catania</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>77</v>
+      </c>
+      <c r="K10" t="n">
+        <v>773</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>bHLf4sq9</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45507.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vanni sanna
+  sassari </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>UiGfvfvT</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>torres</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>mantova</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>77</v>
+      </c>
+      <c r="K11" t="n">
+        <v>773</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>WlhYT07d</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45508.54166666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio romeo menti
+  castellammare di stabia </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>juve stabia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>A332L1f5</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>avellino</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>77</v>
+      </c>
+      <c r="K12" t="n">
+        <v>773</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SzxylMbS</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45508.64583333334</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>cesena</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2gUwEtrE</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>padova</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>77</v>
+      </c>
+      <c r="K13" t="n">
+        <v>773</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>QT6wuRFc</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45513.54166666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>sassuolo</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>cittadella</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>77</v>
+      </c>
+      <c r="K14" t="n">
+        <v>773</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>hvcjgHz8</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45513.65625</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>reggiana</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>77</v>
+      </c>
+      <c r="K15" t="n">
+        <v>773</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AZ3PVMxp</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45513.67708333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brianteo
+  monza </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>16917</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>sudtirol</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>77</v>
+      </c>
+      <c r="K16" t="n">
+        <v>773</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>bs5ow5pA</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45514.54166666666</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio giovanni zini
+  cremona </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>20641</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>cremonese</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>bari</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>77</v>
+      </c>
+      <c r="K17" t="n">
+        <v>773</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Ob5Zdayq</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45514.65625</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio carlo castellani
+  empoli </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>16284</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>catanzaro</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>77</v>
+      </c>
+      <c r="K18" t="n">
+        <v>773</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dC3sew6e</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45514.67708333334</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio diego armando maradona
+  naples </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>54726</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>modena</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>77</v>
+      </c>
+      <c r="K19" t="n">
+        <v>773</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>6sP22LDL</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45515.54166666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>brescia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>77</v>
+      </c>
+      <c r="K20" t="n">
+        <v>773</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>bepKi4a3</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45515.5625</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio ennio tardini
+  parma </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>27906</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>palermo</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>77</v>
+      </c>
+      <c r="K21" t="n">
+        <v>773</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ILr8tvi2</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45515.65625</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio luigi ferraris
+  genoa </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>36599</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>sampdoria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>77</v>
+      </c>
+      <c r="K22" t="n">
+        <v>773</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>ALOjHNNj</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45515.67708333334</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio olimpico di torino
+  turin </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>28177</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>cosenza</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>77</v>
+      </c>
+      <c r="K23" t="n">
+        <v>773</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Aeu0r0Mk</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45516.54166666666</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>frosinone</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>pisa</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>77</v>
+      </c>
+      <c r="K24" t="n">
+        <v>773</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>fNwTkrUF</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45516.65625</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>salernitana</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>spezia</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>77</v>
+      </c>
+      <c r="K25" t="n">
+        <v>773</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/p6_deployment/data/italy/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/italy/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1003,992 +1003,1729 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
+          <t>t4ZkclrT</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45507.54166666666</v>
+        <v>45523.5625</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
+          <t xml:space="preserve">stadio via del mare
+  lecce </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>40670</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>77</v>
+      </c>
+      <c r="K10" t="n">
+        <v>771</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EirZ0Wr4</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45523.65625</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz stadium
+  turin </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>41507</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>77</v>
+      </c>
+      <c r="K11" t="n">
+        <v>771</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>f9bfyqFM</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45507.54166666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
           <t xml:space="preserve">stadio dei marmi
   carrara </t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E12" t="n">
         <v>5280</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>hG4fg4z3</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>carrarese</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>4rwnnbnB</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>catania</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>77</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="J12" t="n">
+        <v>77</v>
+      </c>
+      <c r="K12" t="n">
         <v>773</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>bHLf4sq9</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
+      <c r="B13" s="2" t="n">
         <v>45507.64583333334</v>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">vanni sanna
   sassari </t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E13" t="n">
         <v>12000</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>UiGfvfvT</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>torres</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>z7WK5Pwb</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>mantova</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>77</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="J13" t="n">
+        <v>77</v>
+      </c>
+      <c r="K13" t="n">
         <v>773</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>WlhYT07d</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B14" s="2" t="n">
         <v>45508.54166666666</v>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio romeo menti
   castellammare di stabia </t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E14" t="n">
         <v>13000</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>hKSfjtsQ</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>juve stabia</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>A332L1f5</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>avellino</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>77</v>
-      </c>
-      <c r="K12" t="n">
+      <c r="J14" t="n">
+        <v>77</v>
+      </c>
+      <c r="K14" t="n">
         <v>773</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="M12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>SzxylMbS</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
+      <c r="B15" s="2" t="n">
         <v>45508.64583333334</v>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio dino manuzzi
   cesena </t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E15" t="n">
         <v>23860</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>xddf1qfh</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>cesena</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>2gUwEtrE</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>padova</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>77</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="J15" t="n">
+        <v>77</v>
+      </c>
+      <c r="K15" t="n">
         <v>773</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="M13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>QT6wuRFc</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B16" s="2" t="n">
         <v>45513.54166666666</v>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">mapei stadium – citta del tricolore
   reggio emilia </t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E16" t="n">
         <v>21525</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>QDdvI0zl</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>sassuolo</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>C0yUqo8c</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>cittadella</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>77</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="J16" t="n">
+        <v>77</v>
+      </c>
+      <c r="K16" t="n">
         <v>773</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
+      <c r="M16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>hvcjgHz8</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
+      <c r="B17" s="2" t="n">
         <v>45513.65625</v>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio luigi ferraris
   genoa </t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E17" t="n">
         <v>36599</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>d0PJxeie</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>genoa</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>6ulJbMCe</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>reggiana</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>77</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="J17" t="n">
+        <v>77</v>
+      </c>
+      <c r="K17" t="n">
         <v>773</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="M15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>AZ3PVMxp</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B18" s="2" t="n">
         <v>45513.67708333334</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">brianteo
   monza </t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E18" t="n">
         <v>16917</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>4YSMlwj7</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>monza</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>W02MZDnp</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>sudtirol</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>77</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="J18" t="n">
+        <v>77</v>
+      </c>
+      <c r="K18" t="n">
         <v>773</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
+      <c r="M18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>bs5ow5pA</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
+      <c r="B19" s="2" t="n">
         <v>45514.54166666666</v>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio giovanni zini
   cremona </t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E19" t="n">
         <v>20641</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>KUzfp5N3</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>cremonese</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>xIkUr2vO</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>bari</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>77</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="J19" t="n">
+        <v>77</v>
+      </c>
+      <c r="K19" t="n">
         <v>773</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="M17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
+      <c r="M19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>Ob5Zdayq</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B20" s="2" t="n">
         <v>45514.65625</v>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio carlo castellani
   empoli </t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E20" t="n">
         <v>16284</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>0ESCnI1H</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>empoli</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>GnizyMB7</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>catanzaro</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>77</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="J20" t="n">
+        <v>77</v>
+      </c>
+      <c r="K20" t="n">
         <v>773</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="M18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
+      <c r="M20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>dC3sew6e</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <v>45514.67708333334</v>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio diego armando maradona
   naples </t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E21" t="n">
         <v>54726</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>69Dxbc61</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>napoli</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>MBn63swN</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>modena</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>77</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="J21" t="n">
+        <v>77</v>
+      </c>
+      <c r="K21" t="n">
         <v>773</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
+      <c r="M21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>6sP22LDL</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B22" s="2" t="n">
         <v>45515.54166666666</v>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio mario rigamonti
   brescia </t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E22" t="n">
         <v>19500</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>jci0qO9B</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>brescia</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>MkPmVv50</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>venezia</t>
         </is>
       </c>
-      <c r="J20" t="n">
-        <v>77</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J22" t="n">
+        <v>77</v>
+      </c>
+      <c r="K22" t="n">
         <v>773</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
+      <c r="M22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>bepKi4a3</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
+      <c r="B23" s="2" t="n">
         <v>45515.5625</v>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio ennio tardini
   parma </t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E23" t="n">
         <v>27906</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>6DxlaxHN</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>parma</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>n38Nktmn</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>palermo</t>
         </is>
       </c>
-      <c r="J21" t="n">
-        <v>77</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="J23" t="n">
+        <v>77</v>
+      </c>
+      <c r="K23" t="n">
         <v>773</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="M23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>ILr8tvi2</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
+      <c r="B24" s="2" t="n">
         <v>45515.65625</v>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio luigi ferraris
   genoa </t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E24" t="n">
         <v>36599</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>nJbCGx2U</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>sampdoria</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>ttyLthOA</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>como</t>
         </is>
       </c>
-      <c r="J22" t="n">
-        <v>77</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="J24" t="n">
+        <v>77</v>
+      </c>
+      <c r="K24" t="n">
         <v>773</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="M22" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
+      <c r="M24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>ALOjHNNj</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n">
+      <c r="B25" s="2" t="n">
         <v>45515.67708333334</v>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio olimpico di torino
   turin </t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E25" t="n">
         <v>28177</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>MZFZnvX4</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>torino</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>p84TeBhA</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>cosenza</t>
         </is>
       </c>
-      <c r="J23" t="n">
-        <v>77</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="J25" t="n">
+        <v>77</v>
+      </c>
+      <c r="K25" t="n">
         <v>773</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="M23" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
+      <c r="M25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>Aeu0r0Mk</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B26" s="2" t="n">
         <v>45516.54166666666</v>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio benito stirpe
   frosinone </t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E26" t="n">
         <v>16227</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>pfo9H1Wp</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>frosinone</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>roasMsOT</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>pisa</t>
         </is>
       </c>
-      <c r="J24" t="n">
-        <v>77</v>
-      </c>
-      <c r="K24" t="n">
+      <c r="J26" t="n">
+        <v>77</v>
+      </c>
+      <c r="K26" t="n">
         <v>773</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="M24" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="M26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>coppa italia</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>fNwTkrUF</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
+      <c r="B27" s="2" t="n">
         <v>45516.65625</v>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t xml:space="preserve">stadio arechi
   salerno </t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E27" t="n">
         <v>37800</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Mq05g4BP</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>salernitana</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>re6VD39b</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>spezia</t>
         </is>
       </c>
-      <c r="J25" t="n">
-        <v>77</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="J27" t="n">
+        <v>77</v>
+      </c>
+      <c r="K27" t="n">
         <v>773</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="M25" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
+      <c r="M27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>coppa italia</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45520.64583333334</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio mario rigamonti
+  brescia </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>jci0qO9B</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>brescia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>n38Nktmn</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>palermo</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>77</v>
+      </c>
+      <c r="K28" t="n">
+        <v>774</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san nicola
+  bari </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>58270</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>xIkUr2vO</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>bari</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>hKSfjtsQ</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>juve stabia</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>77</v>
+      </c>
+      <c r="K29" t="n">
+        <v>774</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arena garibaldi   stadio romeo anconetani
+  pisa </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>14869</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>roasMsOT</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>pisa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>re6VD39b</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>spezia</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>77</v>
+      </c>
+      <c r="K30" t="n">
+        <v>774</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio arechi
+  salerno </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>37800</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mq05g4BP</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>salernitana</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>C0yUqo8c</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>cittadella</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>77</v>
+      </c>
+      <c r="K31" t="n">
+        <v>774</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio marco druso
+  bolzano </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5539</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>W02MZDnp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>sudtirol</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>MBn63swN</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>modena</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>77</v>
+      </c>
+      <c r="K32" t="n">
+        <v>774</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>GnizyMB7</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>catanzaro</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>QDdvI0zl</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>sassuolo</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>77</v>
+      </c>
+      <c r="K33" t="n">
+        <v>774</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>23860</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>xddf1qfh</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>cesena</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>hG4fg4z3</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>carrarese</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>77</v>
+      </c>
+      <c r="K34" t="n">
+        <v>774</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio san vito luigi marulla
+  cosenza </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>20987</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>p84TeBhA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>cosenza</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>KUzfp5N3</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>cremonese</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>77</v>
+      </c>
+      <c r="K35" t="n">
+        <v>774</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadio benito stirpe
+  frosinone </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>16227</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>pfo9H1Wp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>frosinone</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>nJbCGx2U</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>sampdoria</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>77</v>
+      </c>
+      <c r="K36" t="n">
+        <v>774</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>IXMN9zkI</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mapei stadium – citta del tricolore
+  reggio emilia </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>21525</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>6ulJbMCe</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>reggiana</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>z7WK5Pwb</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>mantova</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>77</v>
+      </c>
+      <c r="K37" t="n">
+        <v>774</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>serie b</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/italy/data_preparation/clean_data/df_match_cleaned.xlsx
+++ b/p6_deployment/data/italy/data_preparation/clean_data/df_match_cleaned.xlsx
@@ -1251,40 +1251,40 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>SzxylMbS</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45508.54166666666</v>
+        <v>45508.64583333334</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio romeo menti
-  castellammare di stabia </t>
+          <t xml:space="preserve">stadio dino manuzzi
+  cesena </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13000</v>
+        <v>23860</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>hKSfjtsQ</t>
+          <t>xddf1qfh</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>juve stabia</t>
+          <t>cesena</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>A332L1f5</t>
+          <t>2gUwEtrE</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>avellino</t>
+          <t>padova</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1313,40 +1313,40 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>WlhYT07d</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45508.64583333334</v>
+        <v>45508.65625</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadio dino manuzzi
-  cesena </t>
+          <t xml:space="preserve">stadio partenio adriano lombardi
+  avellino </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>23860</v>
+        <v>26000</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>xddf1qfh</t>
+          <t>A332L1f5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>cesena</t>
+          <t>avellino</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2gUwEtrE</t>
+          <t>hKSfjtsQ</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>padova</t>
+          <t>juve stabia</t>
         </is>
       </c>
       <c r="J15" t="n">
